--- a/projeto/categorias_nibo.xlsx
+++ b/projeto/categorias_nibo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\projeto_atendimento\NIBO WEB API\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86C1835-825D-4375-AE73-D8C2287DAEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E240090-590A-48F8-BD25-5665A6F0A540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Categoria" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>ID</t>
   </si>
@@ -89,13 +89,19 @@
   </si>
   <si>
     <t>Vale Transporte 3212609</t>
+  </si>
+  <si>
+    <t>Adiantamento Salarial</t>
+  </si>
+  <si>
+    <t>bfce20b7-4cff-436b-877b-535237d3d0b3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,6 +113,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -147,10 +159,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -456,14 +471,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="42.53125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -471,7 +486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -479,7 +494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -487,7 +502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -495,7 +510,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -503,7 +518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -511,7 +526,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -519,7 +534,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -527,7 +542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -535,7 +550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -543,12 +558,20 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>21</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/projeto/categorias_nibo.xlsx
+++ b/projeto/categorias_nibo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E240090-590A-48F8-BD25-5665A6F0A540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F22E766-4458-4D5B-BEC2-856E692DB8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15274" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Categoria" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -95,6 +95,30 @@
   </si>
   <si>
     <t>bfce20b7-4cff-436b-877b-535237d3d0b3</t>
+  </si>
+  <si>
+    <t>Cofins a Recolher 2131110</t>
+  </si>
+  <si>
+    <t>8ca3961d-1800-480e-841d-27ebb6e0cbca</t>
+  </si>
+  <si>
+    <t>PIS a Recolher 21311109</t>
+  </si>
+  <si>
+    <t>7b7646ae-2a9b-4d5c-8045-2e9ee20f128c</t>
+  </si>
+  <si>
+    <t>Seguro Sindical Folha 3221405</t>
+  </si>
+  <si>
+    <t>bc6252fc-8a49-45de-94c8-fe68a2ef3baf</t>
+  </si>
+  <si>
+    <t>Benefícios Social Sindicato 3221405</t>
+  </si>
+  <si>
+    <t>2a456809-2058-43cf-9610-b2ae249dae67</t>
   </si>
 </sst>
 </file>
@@ -471,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="42.53515625" bestFit="1" customWidth="1"/>
@@ -574,6 +598,38 @@
         <v>23</v>
       </c>
     </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B11" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
